--- a/astro-site/public/dl/kit-tareas-catering/07-plantilla-personalizable.xlsx
+++ b/astro-site/public/dl/kit-tareas-catering/07-plantilla-personalizable.xlsx
@@ -1,18 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Por Fase" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Por Zona" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Por Perfil" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por Fase" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por Zona" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por Perfil" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Por Fase'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Por Zona'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Por Perfil'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -112,31 +116,41 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -496,15 +510,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -512,6 +527,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -540,9 +556,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -564,8 +578,25 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-catering · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -574,18 +605,18 @@
   <sheetPr>
     <tabColor rgb="00E0F2F1"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -602,6 +633,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1194,12 +1226,26 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G54">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 E52 E53 E54" type="list">
+    <dataValidation sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 E52 E53 E54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1208,18 +1254,18 @@
   <sheetPr>
     <tabColor rgb="00F3E5F5"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1236,6 +1282,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1828,12 +1875,26 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G54">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 E52 E53 E54" type="list">
+    <dataValidation sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 E52 E53 E54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1842,18 +1903,18 @@
   <sheetPr>
     <tabColor rgb="00E8F5E9"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1870,6 +1931,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -2462,11 +2524,25 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G54">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 E52 E53 E54" type="list">
+    <dataValidation sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 E52 E53 E54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-catering/07-plantilla-personalizable.xlsx
+++ b/astro-site/public/dl/kit-tareas-catering/07-plantilla-personalizable.xlsx
@@ -512,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -582,7 +582,14 @@
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-catering · info@aichef.pro</t>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-catering · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -1232,8 +1239,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 E52 E53 E54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 E52 E53 E54" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1881,8 +1888,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 E52 E53 E54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 E52 E53 E54" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -2530,8 +2537,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 E52 E53 E54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 E23 E24 E25 E26 E27 E28 E29 E30 E31 E32 E33 E34 E35 E36 E37 E38 E39 E40 E41 E42 E43 E44 E45 E46 E47 E48 E49 E50 E51 E52 E53 E54" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
